--- a/research/phase-3/Phase_3_Competitor_Channel_Map.xlsx
+++ b/research/phase-3/Phase_3_Competitor_Channel_Map.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Map" sheetId="1" r:id="R2ba149321b0d4110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Map" sheetId="1" r:id="R8ab21b6afb0142d0"/>
   </x:sheets>
 </x:workbook>
 </file>
